--- a/qualificacao_doutorado/dados_qualificacao_doutorado.xlsx
+++ b/qualificacao_doutorado/dados_qualificacao_doutorado.xlsx
@@ -735,7 +735,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fonte Título: opcional, entre 8 e 36 pontos; 21 reproduz o exemplo.</t>
+          <t>Fonte Título: tamanho máximo opcional entre 8 e 36 pontos. A fonte diminui automaticamente para caber na caixa.</t>
         </is>
       </c>
     </row>
